--- a/ns-3.45/result_csv/cu_0112.xlsx
+++ b/ns-3.45/result_csv/cu_0112.xlsx
@@ -1,45 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11130"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10110"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kamikawamasahiro/Desktop/ns-allinone-3.45/ns-3.45/result_csv/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kamikawa/Desktop/ns-allinone-3.45/ns-3.45/result_csv/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE765222-DBDC-B74F-8FB0-651CB0A13751}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{667C2A3C-D0CB-5A4B-9B6B-978F3BC20BCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28320" yWindow="180" windowWidth="28300" windowHeight="16740" xr2:uid="{38F26BCD-736D-C746-9F00-1E53149B111B}"/>
+    <workbookView xWindow="38400" yWindow="600" windowWidth="38400" windowHeight="21000" xr2:uid="{38F26BCD-736D-C746-9F00-1E53149B111B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlchart.v1.0" hidden="1">Sheet1!$K$1</definedName>
-    <definedName name="_xlchart.v1.1" hidden="1">Sheet1!$K$15:$K$25</definedName>
-    <definedName name="_xlchart.v1.10" hidden="1">Sheet1!$K$2:$K$13</definedName>
-    <definedName name="_xlchart.v1.11" hidden="1">Sheet1!$S$15:$S$25</definedName>
-    <definedName name="_xlchart.v1.12" hidden="1">Sheet1!$S$27:$S$35</definedName>
-    <definedName name="_xlchart.v1.13" hidden="1">Sheet1!$S$2:$S$13</definedName>
-    <definedName name="_xlchart.v1.14" hidden="1">Sheet1!$K$1</definedName>
-    <definedName name="_xlchart.v1.15" hidden="1">Sheet1!$K$15:$K$25</definedName>
-    <definedName name="_xlchart.v1.16" hidden="1">Sheet1!$K$27:$K$35</definedName>
-    <definedName name="_xlchart.v1.17" hidden="1">Sheet1!$K$2:$K$13</definedName>
-    <definedName name="_xlchart.v1.18" hidden="1">Sheet1!$S$15:$S$25</definedName>
-    <definedName name="_xlchart.v1.19" hidden="1">Sheet1!$S$27:$S$35</definedName>
-    <definedName name="_xlchart.v1.2" hidden="1">Sheet1!$K$27:$K$35</definedName>
-    <definedName name="_xlchart.v1.20" hidden="1">Sheet1!$S$2:$S$13</definedName>
-    <definedName name="_xlchart.v1.3" hidden="1">Sheet1!$K$2:$K$13</definedName>
-    <definedName name="_xlchart.v1.4" hidden="1">Sheet1!$S$15:$S$25</definedName>
-    <definedName name="_xlchart.v1.5" hidden="1">Sheet1!$S$27:$S$35</definedName>
-    <definedName name="_xlchart.v1.6" hidden="1">Sheet1!$S$2:$S$13</definedName>
-    <definedName name="_xlchart.v1.7" hidden="1">Sheet1!$K$1</definedName>
-    <definedName name="_xlchart.v1.8" hidden="1">Sheet1!$K$15:$K$25</definedName>
-    <definedName name="_xlchart.v1.9" hidden="1">Sheet1!$K$27:$K$35</definedName>
-  </definedNames>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -60,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="37">
   <si>
     <t>Stations</t>
   </si>
@@ -2509,6 +2486,1136 @@
           </a:p>
         </c:txPr>
         <c:crossAx val="1504297408"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="ja-JP"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart14.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="ja-JP"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ja-JP"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$K$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>LossRate(%)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Sheet1!$P$2:$P$13</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>5.0748300000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2.8186200000000001</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.63964200000000004</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>4.5726500000000003</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1.37141</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.94703899999999996</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>7.4445899999999998</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1.6297900000000001</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>51.054499999999997</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2.1684899999999998</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>2.9212699999999998</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Sheet1!$K$2:$K$13</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>37.916800000000002</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>37.959200000000003</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>45.009300000000003</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>52.0764</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>54.4694</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>61.093200000000003</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>69.265100000000004</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>71.428899999999999</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>78.9529</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>86.288700000000006</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>84.135999999999996</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>85.345100000000002</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-F1E7-F742-AE76-CA8DFF18020D}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="1601798144"/>
+        <c:axId val="1612091776"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="1601798144"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ja-JP"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1612091776"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="1612091776"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ja-JP"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1601798144"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="ja-JP"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart15.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="ja-JP"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ja-JP"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$I$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Utilization(%)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Sheet1!$P$2:$P$13</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>5.0748300000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2.8186200000000001</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.63964200000000004</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>4.5726500000000003</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1.37141</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.94703899999999996</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>7.4445899999999998</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1.6297900000000001</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>51.054499999999997</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2.1684899999999998</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>2.9212699999999998</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Sheet1!$I$2:$I$13</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>88.979399999999998</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>88.964600000000004</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>89.128900000000002</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>90.739000000000004</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>90.171899999999994</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>91.762100000000004</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>92.943399999999997</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>92.346299999999999</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>94.153800000000004</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>92.466999999999999</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>94.687700000000007</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>94.642399999999995</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-3E77-7F4F-B1A3-FA7D656CE370}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="1640772736"/>
+        <c:axId val="1568349184"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="1640772736"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ja-JP"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1568349184"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="1568349184"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ja-JP"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1640772736"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="ja-JP"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart16.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="ja-JP"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="ja-JP" altLang="en-US"/>
+              <a:t>ロス率とチャネル使用率</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ja-JP"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Sheet1!$K$2:$K$13</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>37.916800000000002</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>37.959200000000003</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>45.009300000000003</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>52.0764</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>54.4694</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>61.093200000000003</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>69.265100000000004</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>71.428899999999999</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>78.9529</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>86.288700000000006</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>84.135999999999996</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>85.345100000000002</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Sheet1!$I$2:$I$13</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>88.979399999999998</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>88.964600000000004</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>89.128900000000002</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>90.739000000000004</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>90.171899999999994</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>91.762100000000004</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>92.943399999999997</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>92.346299999999999</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>94.153800000000004</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>92.466999999999999</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>94.687700000000007</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>94.642399999999995</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-2DC0-7143-885E-DEAC40B53C99}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="1568661376"/>
+        <c:axId val="1568659136"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="1568661376"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ja-JP"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1568659136"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="1568659136"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ja-JP"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1568661376"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -6142,6 +7249,126 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors13.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors14.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors15.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="13">
   <a:schemeClr val="accent6"/>
@@ -7987,6 +9214,1554 @@
 </file>
 
 <file path=xl/charts/style12.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style13.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style14.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style15.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -13052,16 +15827,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>143931</xdr:colOff>
-      <xdr:row>39</xdr:row>
-      <xdr:rowOff>84665</xdr:rowOff>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>25400</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>203198</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>922865</xdr:colOff>
-      <xdr:row>50</xdr:row>
-      <xdr:rowOff>33865</xdr:rowOff>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>635000</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>152398</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -13088,16 +15863,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>821267</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>152400</xdr:rowOff>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>855134</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>50800</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>702733</xdr:colOff>
-      <xdr:row>25</xdr:row>
-      <xdr:rowOff>101600</xdr:rowOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>685800</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -13117,6 +15892,114 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId13"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>287867</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>169334</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>372534</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>118534</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="グラフ 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{86952B1B-205A-0BA1-9222-EE3E203AD1FE}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId14"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>541868</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>203200</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>524934</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="グラフ 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E2E58A67-25F9-79F0-E53B-77AA1A6E0029}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId15"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>1117601</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>186266</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>999067</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>135466</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="4" name="グラフ 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9177D1BD-4E3E-8937-E8DE-25F2A732CD87}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId16"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -13442,7 +16325,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{981411BD-1072-6F43-B943-37506282C879}">
-  <dimension ref="A1:AC35"/>
+  <dimension ref="A1:AC51"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20"/>
   <cols>
     <col min="9" max="9" width="12.5703125" customWidth="1"/>
@@ -15984,6 +18867,257 @@
         <v>7.7057099999999998</v>
       </c>
     </row>
+    <row r="39" spans="1:20">
+      <c r="E39">
+        <v>200</v>
+      </c>
+      <c r="L39" t="s">
+        <v>10</v>
+      </c>
+      <c r="M39" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="40" spans="1:20">
+      <c r="B40">
+        <f>35+(55/(1+EXP(0.23*($S2+70.5))))</f>
+        <v>35.707101845328204</v>
+      </c>
+      <c r="C40">
+        <v>37.916800000000002</v>
+      </c>
+      <c r="E40">
+        <v>5.2989700000000001E-2</v>
+      </c>
+      <c r="F40">
+        <v>1.9715499999999999</v>
+      </c>
+      <c r="L40">
+        <v>37.916800000000002</v>
+      </c>
+      <c r="M40">
+        <v>-51.626199999999997</v>
+      </c>
+    </row>
+    <row r="41" spans="1:20">
+      <c r="B41">
+        <f t="shared" ref="B41:B51" si="6">35+(55/(1+EXP(0.23*($S3+70.5))))</f>
+        <v>40.17880106514658</v>
+      </c>
+      <c r="C41">
+        <v>37.959200000000003</v>
+      </c>
+      <c r="E41">
+        <v>5.25773E-2</v>
+      </c>
+      <c r="F41">
+        <v>1.9762200000000001</v>
+      </c>
+      <c r="L41">
+        <v>37.959200000000003</v>
+      </c>
+      <c r="M41">
+        <v>-60.6571</v>
+      </c>
+    </row>
+    <row r="42" spans="1:20">
+      <c r="B42">
+        <f t="shared" si="6"/>
+        <v>44.276037823493652</v>
+      </c>
+      <c r="C42">
+        <v>45.009300000000003</v>
+      </c>
+      <c r="E42">
+        <v>5.2783499999999997E-2</v>
+      </c>
+      <c r="F42">
+        <v>20.127300000000002</v>
+      </c>
+      <c r="L42">
+        <v>45.009300000000003</v>
+      </c>
+      <c r="M42">
+        <v>-63.564399999999999</v>
+      </c>
+    </row>
+    <row r="43" spans="1:20">
+      <c r="B43">
+        <f t="shared" si="6"/>
+        <v>49.269571913171582</v>
+      </c>
+      <c r="C43">
+        <v>52.0764</v>
+      </c>
+      <c r="E43">
+        <v>5.4020600000000002E-2</v>
+      </c>
+      <c r="F43">
+        <v>35.155299999999997</v>
+      </c>
+      <c r="L43">
+        <v>52.0764</v>
+      </c>
+      <c r="M43">
+        <v>-65.939800000000005</v>
+      </c>
+    </row>
+    <row r="44" spans="1:20">
+      <c r="B44">
+        <f t="shared" si="6"/>
+        <v>54.653878136680746</v>
+      </c>
+      <c r="C44">
+        <v>54.4694</v>
+      </c>
+      <c r="E44">
+        <v>6.9690699999999994E-2</v>
+      </c>
+      <c r="F44">
+        <v>48.775100000000002</v>
+      </c>
+      <c r="L44">
+        <v>54.4694</v>
+      </c>
+      <c r="M44">
+        <v>-67.9482</v>
+      </c>
+    </row>
+    <row r="45" spans="1:20">
+      <c r="B45">
+        <f t="shared" si="6"/>
+        <v>59.939488081925525</v>
+      </c>
+      <c r="C45">
+        <v>61.093200000000003</v>
+      </c>
+      <c r="E45">
+        <v>9.2783500000000005E-2</v>
+      </c>
+      <c r="F45">
+        <v>52.381399999999999</v>
+      </c>
+      <c r="L45">
+        <v>61.093200000000003</v>
+      </c>
+      <c r="M45">
+        <v>-69.688000000000002</v>
+      </c>
+    </row>
+    <row r="46" spans="1:20">
+      <c r="B46">
+        <f t="shared" si="6"/>
+        <v>69.001050389202106</v>
+      </c>
+      <c r="C46">
+        <v>69.265100000000004</v>
+      </c>
+      <c r="E46">
+        <v>0.39340199999999997</v>
+      </c>
+      <c r="F46">
+        <v>64.921499999999995</v>
+      </c>
+      <c r="L46">
+        <v>69.265100000000004</v>
+      </c>
+      <c r="M46">
+        <v>-72.595299999999995</v>
+      </c>
+    </row>
+    <row r="47" spans="1:20">
+      <c r="B47">
+        <f t="shared" si="6"/>
+        <v>75.511823854559651</v>
+      </c>
+      <c r="C47">
+        <v>71.428899999999999</v>
+      </c>
+      <c r="E47">
+        <v>0.40020600000000001</v>
+      </c>
+      <c r="F47">
+        <v>77.147800000000004</v>
+      </c>
+      <c r="L47">
+        <v>71.428899999999999</v>
+      </c>
+      <c r="M47">
+        <v>-74.970699999999994</v>
+      </c>
+    </row>
+    <row r="48" spans="1:20">
+      <c r="B48">
+        <f t="shared" si="6"/>
+        <v>79.885898148124113</v>
+      </c>
+      <c r="C48">
+        <v>78.9529</v>
+      </c>
+      <c r="E48">
+        <v>2.8183500000000001</v>
+      </c>
+      <c r="F48">
+        <v>75.575100000000006</v>
+      </c>
+      <c r="L48">
+        <v>78.9529</v>
+      </c>
+      <c r="M48">
+        <v>-76.979100000000003</v>
+      </c>
+    </row>
+    <row r="49" spans="2:13">
+      <c r="B49">
+        <f t="shared" si="6"/>
+        <v>82.783729961910851</v>
+      </c>
+      <c r="C49">
+        <v>86.288700000000006</v>
+      </c>
+      <c r="E49">
+        <v>23.162700000000001</v>
+      </c>
+      <c r="L49">
+        <v>86.288700000000006</v>
+      </c>
+      <c r="M49">
+        <v>-78.718900000000005</v>
+      </c>
+    </row>
+    <row r="50" spans="2:13">
+      <c r="B50">
+        <f t="shared" si="6"/>
+        <v>83.848479690808773</v>
+      </c>
+      <c r="C50">
+        <v>84.135999999999996</v>
+      </c>
+      <c r="E50">
+        <v>47.382300000000001</v>
+      </c>
+      <c r="L50">
+        <v>84.135999999999996</v>
+      </c>
+      <c r="M50">
+        <v>-79.508799999999994</v>
+      </c>
+    </row>
+    <row r="51" spans="2:13">
+      <c r="B51">
+        <f t="shared" si="6"/>
+        <v>84.723930936036908</v>
+      </c>
+      <c r="C51">
+        <v>85.345100000000002</v>
+      </c>
+      <c r="L51">
+        <v>85.345100000000002</v>
+      </c>
+      <c r="M51">
+        <v>-80.253500000000003</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/ns-3.45/result_csv/cu_0112.xlsx
+++ b/ns-3.45/result_csv/cu_0112.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10110"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11130"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kamikawa/Desktop/ns-allinone-3.45/ns-3.45/result_csv/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kamikawamasahiro/Desktop/ns-allinone-3.45/ns-3.45/result_csv/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{667C2A3C-D0CB-5A4B-9B6B-978F3BC20BCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D624C204-816E-0D4A-AA2F-7F5CF6D9326E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38400" yWindow="600" windowWidth="38400" windowHeight="21000" xr2:uid="{38F26BCD-736D-C746-9F00-1E53149B111B}"/>
+    <workbookView xWindow="820" yWindow="620" windowWidth="28800" windowHeight="16260" xr2:uid="{38F26BCD-736D-C746-9F00-1E53149B111B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="37">
   <si>
     <t>Stations</t>
   </si>
@@ -1539,24 +1539,22 @@
     <c:title>
       <c:tx>
         <c:rich>
-          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:bodyPr rot="0" vert="horz"/>
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
+              <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:rPr lang="en-US" altLang="ja-JP"/>
+              <a:rPr lang="en-US"/>
+              <a:t>RSSI</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="ja-JP"/>
+              <a:t>と</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US"/>
               <a:t>LossRate(%)</a:t>
             </a:r>
           </a:p>
@@ -2060,21 +2058,11 @@
           <a:effectLst/>
         </c:spPr>
         <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:bodyPr rot="-60000000" vert="horz"/>
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
+              <a:defRPr/>
             </a:pPr>
             <a:endParaRPr lang="ja-JP"/>
           </a:p>
@@ -2122,21 +2110,11 @@
           <a:effectLst/>
         </c:spPr>
         <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:bodyPr rot="-60000000" vert="horz"/>
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
+              <a:defRPr/>
             </a:pPr>
             <a:endParaRPr lang="ja-JP"/>
           </a:p>
@@ -2156,7 +2134,7 @@
     <a:lstStyle/>
     <a:p>
       <a:pPr>
-        <a:defRPr/>
+        <a:defRPr sz="1800"/>
       </a:pPr>
       <a:endParaRPr lang="ja-JP"/>
     </a:p>
@@ -2197,7 +2175,7 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+            <a:defRPr sz="2160" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
               <a:solidFill>
                 <a:schemeClr val="tx1">
                   <a:lumMod val="65000"/>
@@ -2408,7 +2386,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="1800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1">
                     <a:lumMod val="65000"/>
@@ -2470,7 +2448,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="1800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1">
                     <a:lumMod val="65000"/>
@@ -2528,7 +2506,7 @@
     <a:lstStyle/>
     <a:p>
       <a:pPr>
-        <a:defRPr/>
+        <a:defRPr sz="1800"/>
       </a:pPr>
       <a:endParaRPr lang="ja-JP"/>
     </a:p>
@@ -2556,6 +2534,39 @@
   </mc:AlternateContent>
   <c:chart>
     <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="2400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Utilization</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="ja-JP"/>
+              <a:t>と再送率</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>(%)</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -2569,7 +2580,7 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+            <a:defRPr sz="2400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
               <a:solidFill>
                 <a:schemeClr val="tx1">
                   <a:lumMod val="65000"/>
@@ -2596,11 +2607,11 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$K$1</c:f>
+              <c:f>Sheet1!$I$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>LossRate(%)</c:v>
+                  <c:v>Utilization(%)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -2676,45 +2687,45 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Sheet1!$K$2:$K$13</c:f>
+              <c:f>Sheet1!$I$2:$I$13</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="12"/>
                 <c:pt idx="0">
-                  <c:v>37.916800000000002</c:v>
+                  <c:v>88.979399999999998</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>37.959200000000003</c:v>
+                  <c:v>88.964600000000004</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>45.009300000000003</c:v>
+                  <c:v>89.128900000000002</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>52.0764</c:v>
+                  <c:v>90.739000000000004</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>54.4694</c:v>
+                  <c:v>90.171899999999994</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>61.093200000000003</c:v>
+                  <c:v>91.762100000000004</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>69.265100000000004</c:v>
+                  <c:v>92.943399999999997</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>71.428899999999999</c:v>
+                  <c:v>92.346299999999999</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>78.9529</c:v>
+                  <c:v>94.153800000000004</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>86.288700000000006</c:v>
+                  <c:v>92.466999999999999</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>84.135999999999996</c:v>
+                  <c:v>94.687700000000007</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>85.345100000000002</c:v>
+                  <c:v>94.642399999999995</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2722,7 +2733,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-F1E7-F742-AE76-CA8DFF18020D}"/>
+              <c16:uniqueId val="{00000000-8D9E-034A-841D-048B24E18642}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2734,11 +2745,11 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:axId val="1601798144"/>
-        <c:axId val="1612091776"/>
+        <c:axId val="1504297408"/>
+        <c:axId val="1313062208"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="1601798144"/>
+        <c:axId val="1504297408"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2758,6 +2769,65 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="2000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t> </a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="ja-JP"/>
+                  <a:t>再送率</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="2000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="ja-JP"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
@@ -2780,7 +2850,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="2000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1">
                     <a:lumMod val="65000"/>
@@ -2795,12 +2865,12 @@
             <a:endParaRPr lang="ja-JP"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1612091776"/>
+        <c:crossAx val="1313062208"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="1612091776"/>
+        <c:axId val="1313062208"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2820,6 +2890,61 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="2000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="ja-JP"/>
+                  <a:t>チャネル使用率</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="2000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="ja-JP"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
@@ -2842,7 +2967,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="2000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1">
                     <a:lumMod val="65000"/>
@@ -2857,7 +2982,7 @@
             <a:endParaRPr lang="ja-JP"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1601798144"/>
+        <c:crossAx val="1504297408"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -2900,765 +3025,7 @@
     <a:lstStyle/>
     <a:p>
       <a:pPr>
-        <a:defRPr/>
-      </a:pPr>
-      <a:endParaRPr lang="ja-JP"/>
-    </a:p>
-  </c:txPr>
-  <c:printSettings>
-    <c:headerFooter/>
-    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
-    <c:pageSetup/>
-  </c:printSettings>
-</c:chartSpace>
-</file>
-
-<file path=xl/charts/chart15.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-  <c:date1904 val="0"/>
-  <c:lang val="ja-JP"/>
-  <c:roundedCorners val="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="102"/>
-    </mc:Choice>
-    <mc:Fallback>
-      <c:style val="2"/>
-    </mc:Fallback>
-  </mc:AlternateContent>
-  <c:chart>
-    <c:title>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="ja-JP"/>
-        </a:p>
-      </c:txPr>
-    </c:title>
-    <c:autoTitleDeleted val="0"/>
-    <c:plotArea>
-      <c:layout/>
-      <c:scatterChart>
-        <c:scatterStyle val="lineMarker"/>
-        <c:varyColors val="0"/>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="0"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Sheet1!$I$1</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Utilization(%)</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="19050" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
-          <c:xVal>
-            <c:numRef>
-              <c:f>Sheet1!$P$2:$P$13</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="12"/>
-                <c:pt idx="0">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>5.0748300000000003E-2</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>2.8186200000000001</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.63964200000000004</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>4.5726500000000003</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>1.37141</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>0.94703899999999996</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>7.4445899999999998</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>1.6297900000000001</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>51.054499999999997</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>2.1684899999999998</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>2.9212699999999998</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>Sheet1!$I$2:$I$13</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="12"/>
-                <c:pt idx="0">
-                  <c:v>88.979399999999998</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>88.964600000000004</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>89.128900000000002</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>90.739000000000004</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>90.171899999999994</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>91.762100000000004</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>92.943399999999997</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>92.346299999999999</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>94.153800000000004</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>92.466999999999999</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>94.687700000000007</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>94.642399999999995</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-3E77-7F4F-B1A3-FA7D656CE370}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:dLbls>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
-        <c:axId val="1640772736"/>
-        <c:axId val="1568349184"/>
-      </c:scatterChart>
-      <c:valAx>
-        <c:axId val="1640772736"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="b"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="25000"/>
-                <a:lumOff val="75000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="ja-JP"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="1568349184"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="midCat"/>
-      </c:valAx>
-      <c:valAx>
-        <c:axId val="1568349184"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="l"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="25000"/>
-                <a:lumOff val="75000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="ja-JP"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="1640772736"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="midCat"/>
-      </c:valAx>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-    </c:plotArea>
-    <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
-    <c:extLst>
-      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
-        <c16r3:dataDisplayOptions16>
-          <c16r3:dispNaAsBlank val="1"/>
-        </c16r3:dataDisplayOptions16>
-      </c:ext>
-    </c:extLst>
-  </c:chart>
-  <c:spPr>
-    <a:solidFill>
-      <a:schemeClr val="bg1"/>
-    </a:solidFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-      <a:solidFill>
-        <a:schemeClr val="tx1">
-          <a:lumMod val="15000"/>
-          <a:lumOff val="85000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:round/>
-    </a:ln>
-    <a:effectLst/>
-  </c:spPr>
-  <c:txPr>
-    <a:bodyPr/>
-    <a:lstStyle/>
-    <a:p>
-      <a:pPr>
-        <a:defRPr/>
-      </a:pPr>
-      <a:endParaRPr lang="ja-JP"/>
-    </a:p>
-  </c:txPr>
-  <c:printSettings>
-    <c:headerFooter/>
-    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
-    <c:pageSetup/>
-  </c:printSettings>
-</c:chartSpace>
-</file>
-
-<file path=xl/charts/chart16.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-  <c:date1904 val="0"/>
-  <c:lang val="ja-JP"/>
-  <c:roundedCorners val="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="102"/>
-    </mc:Choice>
-    <mc:Fallback>
-      <c:style val="2"/>
-    </mc:Fallback>
-  </mc:AlternateContent>
-  <c:chart>
-    <c:title>
-      <c:tx>
-        <c:rich>
-          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:rPr lang="ja-JP" altLang="en-US"/>
-              <a:t>ロス率とチャネル使用率</a:t>
-            </a:r>
-          </a:p>
-        </c:rich>
-      </c:tx>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="ja-JP"/>
-        </a:p>
-      </c:txPr>
-    </c:title>
-    <c:autoTitleDeleted val="0"/>
-    <c:plotArea>
-      <c:layout/>
-      <c:scatterChart>
-        <c:scatterStyle val="lineMarker"/>
-        <c:varyColors val="0"/>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="0"/>
-          <c:spPr>
-            <a:ln w="19050" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
-          <c:xVal>
-            <c:numRef>
-              <c:f>Sheet1!$K$2:$K$13</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="12"/>
-                <c:pt idx="0">
-                  <c:v>37.916800000000002</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>37.959200000000003</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>45.009300000000003</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>52.0764</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>54.4694</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>61.093200000000003</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>69.265100000000004</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>71.428899999999999</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>78.9529</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>86.288700000000006</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>84.135999999999996</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>85.345100000000002</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>Sheet1!$I$2:$I$13</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="12"/>
-                <c:pt idx="0">
-                  <c:v>88.979399999999998</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>88.964600000000004</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>89.128900000000002</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>90.739000000000004</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>90.171899999999994</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>91.762100000000004</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>92.943399999999997</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>92.346299999999999</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>94.153800000000004</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>92.466999999999999</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>94.687700000000007</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>94.642399999999995</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-2DC0-7143-885E-DEAC40B53C99}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:dLbls>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
-        <c:axId val="1568661376"/>
-        <c:axId val="1568659136"/>
-      </c:scatterChart>
-      <c:valAx>
-        <c:axId val="1568661376"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="b"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="25000"/>
-                <a:lumOff val="75000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="ja-JP"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="1568659136"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="midCat"/>
-      </c:valAx>
-      <c:valAx>
-        <c:axId val="1568659136"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="l"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="25000"/>
-                <a:lumOff val="75000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="ja-JP"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="1568661376"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="midCat"/>
-      </c:valAx>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-    </c:plotArea>
-    <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
-    <c:extLst>
-      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
-        <c16r3:dataDisplayOptions16>
-          <c16r3:dispNaAsBlank val="1"/>
-        </c16r3:dataDisplayOptions16>
-      </c:ext>
-    </c:extLst>
-  </c:chart>
-  <c:spPr>
-    <a:solidFill>
-      <a:schemeClr val="bg1"/>
-    </a:solidFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-      <a:solidFill>
-        <a:schemeClr val="tx1">
-          <a:lumMod val="15000"/>
-          <a:lumOff val="85000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:round/>
-    </a:ln>
-    <a:effectLst/>
-  </c:spPr>
-  <c:txPr>
-    <a:bodyPr/>
-    <a:lstStyle/>
-    <a:p>
-      <a:pPr>
-        <a:defRPr/>
+        <a:defRPr sz="2000"/>
       </a:pPr>
       <a:endParaRPr lang="ja-JP"/>
     </a:p>
@@ -7289,86 +6656,6 @@
 </cs:colorStyle>
 </file>
 
-<file path=xl/charts/colors14.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
-  <a:schemeClr val="accent1"/>
-  <a:schemeClr val="accent2"/>
-  <a:schemeClr val="accent3"/>
-  <a:schemeClr val="accent4"/>
-  <a:schemeClr val="accent5"/>
-  <a:schemeClr val="accent6"/>
-  <cs:variation/>
-  <cs:variation>
-    <a:lumMod val="60000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="80000"/>
-    <a:lumOff val="20000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="80000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="60000"/>
-    <a:lumOff val="40000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="50000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="70000"/>
-    <a:lumOff val="30000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="70000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="50000"/>
-    <a:lumOff val="50000"/>
-  </cs:variation>
-</cs:colorStyle>
-</file>
-
-<file path=xl/charts/colors15.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
-  <a:schemeClr val="accent1"/>
-  <a:schemeClr val="accent2"/>
-  <a:schemeClr val="accent3"/>
-  <a:schemeClr val="accent4"/>
-  <a:schemeClr val="accent5"/>
-  <a:schemeClr val="accent6"/>
-  <cs:variation/>
-  <cs:variation>
-    <a:lumMod val="60000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="80000"/>
-    <a:lumOff val="20000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="80000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="60000"/>
-    <a:lumOff val="40000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="50000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="70000"/>
-    <a:lumOff val="30000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="70000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="50000"/>
-    <a:lumOff val="50000"/>
-  </cs:variation>
-</cs:colorStyle>
-</file>
-
 <file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="13">
   <a:schemeClr val="accent6"/>
@@ -9730,1038 +9017,6 @@
 </file>
 
 <file path=xl/charts/style13.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
-  <cs:axisTitle>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1000" kern="1200"/>
-  </cs:axisTitle>
-  <cs:categoryAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:categoryAxis>
-  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="bg1"/>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="1000" kern="1200"/>
-  </cs:chartArea>
-  <cs:dataLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="75000"/>
-        <a:lumOff val="25000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataLabel>
-  <cs:dataLabelCallout>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln>
-        <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
-      <a:spAutoFit/>
-    </cs:bodyPr>
-  </cs:dataLabelCallout>
-  <cs:dataPoint>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:dataPoint>
-  <cs:dataPoint3D>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:dataPoint3D>
-  <cs:dataPointLine>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="19050" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointLine>
-  <cs:dataPointMarker>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointMarker>
-  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
-  <cs:dataPointWireframe>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointWireframe>
-  <cs:dataTable>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataTable>
-  <cs:downBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="dk1">
-          <a:lumMod val="75000"/>
-          <a:lumOff val="25000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:downBar>
-  <cs:dropLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dropLine>
-  <cs:errorBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:errorBar>
-  <cs:floor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
-  </cs:floor>
-  <cs:gridlineMajor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMajor>
-  <cs:gridlineMinor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="5000"/>
-            <a:lumOff val="95000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMinor>
-  <cs:hiLoLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="50000"/>
-            <a:lumOff val="50000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:hiLoLine>
-  <cs:leaderLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:leaderLine>
-  <cs:legend>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:legend>
-  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea>
-  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea3D>
-  <cs:seriesAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:seriesAxis>
-  <cs:seriesLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:seriesLine>
-  <cs:title>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
-  </cs:title>
-  <cs:trendline>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="19050" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:prstDash val="sysDot"/>
-      </a:ln>
-    </cs:spPr>
-  </cs:trendline>
-  <cs:trendlineLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:trendlineLabel>
-  <cs:upBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:upBar>
-  <cs:valueAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:valueAxis>
-  <cs:wall>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
-  </cs:wall>
-</cs:chartStyle>
-</file>
-
-<file path=xl/charts/style14.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
-  <cs:axisTitle>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1000" kern="1200"/>
-  </cs:axisTitle>
-  <cs:categoryAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:categoryAxis>
-  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="bg1"/>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="1000" kern="1200"/>
-  </cs:chartArea>
-  <cs:dataLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="75000"/>
-        <a:lumOff val="25000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataLabel>
-  <cs:dataLabelCallout>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln>
-        <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
-      <a:spAutoFit/>
-    </cs:bodyPr>
-  </cs:dataLabelCallout>
-  <cs:dataPoint>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:dataPoint>
-  <cs:dataPoint3D>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:dataPoint3D>
-  <cs:dataPointLine>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="19050" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointLine>
-  <cs:dataPointMarker>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointMarker>
-  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
-  <cs:dataPointWireframe>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointWireframe>
-  <cs:dataTable>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataTable>
-  <cs:downBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="dk1">
-          <a:lumMod val="75000"/>
-          <a:lumOff val="25000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:downBar>
-  <cs:dropLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dropLine>
-  <cs:errorBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:errorBar>
-  <cs:floor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
-  </cs:floor>
-  <cs:gridlineMajor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMajor>
-  <cs:gridlineMinor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="5000"/>
-            <a:lumOff val="95000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMinor>
-  <cs:hiLoLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="50000"/>
-            <a:lumOff val="50000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:hiLoLine>
-  <cs:leaderLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:leaderLine>
-  <cs:legend>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:legend>
-  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea>
-  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea3D>
-  <cs:seriesAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:seriesAxis>
-  <cs:seriesLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:seriesLine>
-  <cs:title>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
-  </cs:title>
-  <cs:trendline>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="19050" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:prstDash val="sysDot"/>
-      </a:ln>
-    </cs:spPr>
-  </cs:trendline>
-  <cs:trendlineLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:trendlineLabel>
-  <cs:upBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:upBar>
-  <cs:valueAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:valueAxis>
-  <cs:wall>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
-  </cs:wall>
-</cs:chartStyle>
-</file>
-
-<file path=xl/charts/style15.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -15827,16 +14082,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>25400</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>203198</xdr:rowOff>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>787399</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>135464</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>635000</xdr:colOff>
-      <xdr:row>22</xdr:row>
-      <xdr:rowOff>152398</xdr:rowOff>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>270935</xdr:colOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>135467</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -15864,15 +14119,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>855134</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>50800</xdr:rowOff>
+      <xdr:colOff>821268</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>135466</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>685800</xdr:colOff>
-      <xdr:row>38</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>406401</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>253999</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -15899,27 +14154,29 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>287867</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>169334</xdr:rowOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>84666</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>237066</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>18</xdr:col>
-      <xdr:colOff>372534</xdr:colOff>
-      <xdr:row>24</xdr:row>
-      <xdr:rowOff>118534</xdr:rowOff>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>414866</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>101599</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
         <xdr:cNvPr id="2" name="グラフ 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{86952B1B-205A-0BA1-9222-EE3E203AD1FE}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{811B31ED-2A80-FD45-BD0F-CD7259904886}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
-        <xdr:cNvGraphicFramePr/>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="0" y="0"/>
@@ -15928,78 +14185,6 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId14"/>
-        </a:graphicData>
-      </a:graphic>
-    </xdr:graphicFrame>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>541868</xdr:colOff>
-      <xdr:row>26</xdr:row>
-      <xdr:rowOff>203200</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>524934</xdr:colOff>
-      <xdr:row>37</xdr:row>
-      <xdr:rowOff>152400</xdr:rowOff>
-    </xdr:to>
-    <xdr:graphicFrame macro="">
-      <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="3" name="グラフ 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E2E58A67-25F9-79F0-E53B-77AA1A6E0029}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvGraphicFramePr/>
-      </xdr:nvGraphicFramePr>
-      <xdr:xfrm>
-        <a:off x="0" y="0"/>
-        <a:ext cx="0" cy="0"/>
-      </xdr:xfrm>
-      <a:graphic>
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId15"/>
-        </a:graphicData>
-      </a:graphic>
-    </xdr:graphicFrame>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>1117601</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>186266</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>999067</xdr:colOff>
-      <xdr:row>22</xdr:row>
-      <xdr:rowOff>135466</xdr:rowOff>
-    </xdr:to>
-    <xdr:graphicFrame macro="">
-      <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="4" name="グラフ 3">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9177D1BD-4E3E-8937-E8DE-25F2A732CD87}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvGraphicFramePr/>
-      </xdr:nvGraphicFramePr>
-      <xdr:xfrm>
-        <a:off x="0" y="0"/>
-        <a:ext cx="0" cy="0"/>
-      </xdr:xfrm>
-      <a:graphic>
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId16"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -16325,7 +14510,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{981411BD-1072-6F43-B943-37506282C879}">
-  <dimension ref="A1:AC51"/>
+  <dimension ref="A1:AC35"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20"/>
   <cols>
     <col min="9" max="9" width="12.5703125" customWidth="1"/>
@@ -18867,257 +17052,6 @@
         <v>7.7057099999999998</v>
       </c>
     </row>
-    <row r="39" spans="1:20">
-      <c r="E39">
-        <v>200</v>
-      </c>
-      <c r="L39" t="s">
-        <v>10</v>
-      </c>
-      <c r="M39" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="40" spans="1:20">
-      <c r="B40">
-        <f>35+(55/(1+EXP(0.23*($S2+70.5))))</f>
-        <v>35.707101845328204</v>
-      </c>
-      <c r="C40">
-        <v>37.916800000000002</v>
-      </c>
-      <c r="E40">
-        <v>5.2989700000000001E-2</v>
-      </c>
-      <c r="F40">
-        <v>1.9715499999999999</v>
-      </c>
-      <c r="L40">
-        <v>37.916800000000002</v>
-      </c>
-      <c r="M40">
-        <v>-51.626199999999997</v>
-      </c>
-    </row>
-    <row r="41" spans="1:20">
-      <c r="B41">
-        <f t="shared" ref="B41:B51" si="6">35+(55/(1+EXP(0.23*($S3+70.5))))</f>
-        <v>40.17880106514658</v>
-      </c>
-      <c r="C41">
-        <v>37.959200000000003</v>
-      </c>
-      <c r="E41">
-        <v>5.25773E-2</v>
-      </c>
-      <c r="F41">
-        <v>1.9762200000000001</v>
-      </c>
-      <c r="L41">
-        <v>37.959200000000003</v>
-      </c>
-      <c r="M41">
-        <v>-60.6571</v>
-      </c>
-    </row>
-    <row r="42" spans="1:20">
-      <c r="B42">
-        <f t="shared" si="6"/>
-        <v>44.276037823493652</v>
-      </c>
-      <c r="C42">
-        <v>45.009300000000003</v>
-      </c>
-      <c r="E42">
-        <v>5.2783499999999997E-2</v>
-      </c>
-      <c r="F42">
-        <v>20.127300000000002</v>
-      </c>
-      <c r="L42">
-        <v>45.009300000000003</v>
-      </c>
-      <c r="M42">
-        <v>-63.564399999999999</v>
-      </c>
-    </row>
-    <row r="43" spans="1:20">
-      <c r="B43">
-        <f t="shared" si="6"/>
-        <v>49.269571913171582</v>
-      </c>
-      <c r="C43">
-        <v>52.0764</v>
-      </c>
-      <c r="E43">
-        <v>5.4020600000000002E-2</v>
-      </c>
-      <c r="F43">
-        <v>35.155299999999997</v>
-      </c>
-      <c r="L43">
-        <v>52.0764</v>
-      </c>
-      <c r="M43">
-        <v>-65.939800000000005</v>
-      </c>
-    </row>
-    <row r="44" spans="1:20">
-      <c r="B44">
-        <f t="shared" si="6"/>
-        <v>54.653878136680746</v>
-      </c>
-      <c r="C44">
-        <v>54.4694</v>
-      </c>
-      <c r="E44">
-        <v>6.9690699999999994E-2</v>
-      </c>
-      <c r="F44">
-        <v>48.775100000000002</v>
-      </c>
-      <c r="L44">
-        <v>54.4694</v>
-      </c>
-      <c r="M44">
-        <v>-67.9482</v>
-      </c>
-    </row>
-    <row r="45" spans="1:20">
-      <c r="B45">
-        <f t="shared" si="6"/>
-        <v>59.939488081925525</v>
-      </c>
-      <c r="C45">
-        <v>61.093200000000003</v>
-      </c>
-      <c r="E45">
-        <v>9.2783500000000005E-2</v>
-      </c>
-      <c r="F45">
-        <v>52.381399999999999</v>
-      </c>
-      <c r="L45">
-        <v>61.093200000000003</v>
-      </c>
-      <c r="M45">
-        <v>-69.688000000000002</v>
-      </c>
-    </row>
-    <row r="46" spans="1:20">
-      <c r="B46">
-        <f t="shared" si="6"/>
-        <v>69.001050389202106</v>
-      </c>
-      <c r="C46">
-        <v>69.265100000000004</v>
-      </c>
-      <c r="E46">
-        <v>0.39340199999999997</v>
-      </c>
-      <c r="F46">
-        <v>64.921499999999995</v>
-      </c>
-      <c r="L46">
-        <v>69.265100000000004</v>
-      </c>
-      <c r="M46">
-        <v>-72.595299999999995</v>
-      </c>
-    </row>
-    <row r="47" spans="1:20">
-      <c r="B47">
-        <f t="shared" si="6"/>
-        <v>75.511823854559651</v>
-      </c>
-      <c r="C47">
-        <v>71.428899999999999</v>
-      </c>
-      <c r="E47">
-        <v>0.40020600000000001</v>
-      </c>
-      <c r="F47">
-        <v>77.147800000000004</v>
-      </c>
-      <c r="L47">
-        <v>71.428899999999999</v>
-      </c>
-      <c r="M47">
-        <v>-74.970699999999994</v>
-      </c>
-    </row>
-    <row r="48" spans="1:20">
-      <c r="B48">
-        <f t="shared" si="6"/>
-        <v>79.885898148124113</v>
-      </c>
-      <c r="C48">
-        <v>78.9529</v>
-      </c>
-      <c r="E48">
-        <v>2.8183500000000001</v>
-      </c>
-      <c r="F48">
-        <v>75.575100000000006</v>
-      </c>
-      <c r="L48">
-        <v>78.9529</v>
-      </c>
-      <c r="M48">
-        <v>-76.979100000000003</v>
-      </c>
-    </row>
-    <row r="49" spans="2:13">
-      <c r="B49">
-        <f t="shared" si="6"/>
-        <v>82.783729961910851</v>
-      </c>
-      <c r="C49">
-        <v>86.288700000000006</v>
-      </c>
-      <c r="E49">
-        <v>23.162700000000001</v>
-      </c>
-      <c r="L49">
-        <v>86.288700000000006</v>
-      </c>
-      <c r="M49">
-        <v>-78.718900000000005</v>
-      </c>
-    </row>
-    <row r="50" spans="2:13">
-      <c r="B50">
-        <f t="shared" si="6"/>
-        <v>83.848479690808773</v>
-      </c>
-      <c r="C50">
-        <v>84.135999999999996</v>
-      </c>
-      <c r="E50">
-        <v>47.382300000000001</v>
-      </c>
-      <c r="L50">
-        <v>84.135999999999996</v>
-      </c>
-      <c r="M50">
-        <v>-79.508799999999994</v>
-      </c>
-    </row>
-    <row r="51" spans="2:13">
-      <c r="B51">
-        <f t="shared" si="6"/>
-        <v>84.723930936036908</v>
-      </c>
-      <c r="C51">
-        <v>85.345100000000002</v>
-      </c>
-      <c r="L51">
-        <v>85.345100000000002</v>
-      </c>
-      <c r="M51">
-        <v>-80.253500000000003</v>
-      </c>
-    </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
